--- a/artfynd/A 42385-2023 artfynd.xlsx
+++ b/artfynd/A 42385-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42385-2023 artfynd.xlsx
+++ b/artfynd/A 42385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112068040</v>
+        <v>112067161</v>
       </c>
       <c r="B2" t="n">
-        <v>90831</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1599</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469465</v>
+        <v>469256</v>
       </c>
       <c r="R2" t="n">
-        <v>7039571</v>
+        <v>7039724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,51 +776,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112068136</v>
+        <v>112067971</v>
       </c>
       <c r="B3" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469497</v>
+        <v>469443</v>
       </c>
       <c r="R3" t="n">
-        <v>7039592</v>
+        <v>7039562</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,53 +874,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112074141</v>
+        <v>112068040</v>
       </c>
       <c r="B4" t="n">
-        <v>90449</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärnmyren, Nybodarna, Offerdal, Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469230</v>
+        <v>469465</v>
       </c>
       <c r="R4" t="n">
-        <v>7039721</v>
+        <v>7039571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +954,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112068010</v>
+        <v>112068431</v>
       </c>
       <c r="B5" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,35 +983,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469452</v>
+        <v>469560</v>
       </c>
       <c r="R5" t="n">
-        <v>7039595</v>
+        <v>7039585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1090,51 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112067953</v>
+        <v>112370043</v>
       </c>
       <c r="B6" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469442</v>
+        <v>469867</v>
       </c>
       <c r="R6" t="n">
-        <v>7039562</v>
+        <v>7039437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,27 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112067971</v>
+        <v>112074141</v>
       </c>
       <c r="B7" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,35 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Nybodarna, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469442</v>
+        <v>469230</v>
       </c>
       <c r="R7" t="n">
-        <v>7039562</v>
+        <v>7039721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1252,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,53 +1271,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112068431</v>
+        <v>112067953</v>
       </c>
       <c r="B8" t="n">
-        <v>90831</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469560</v>
+        <v>469443</v>
       </c>
       <c r="R8" t="n">
-        <v>7039585</v>
+        <v>7039562</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1351,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,15 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112067161</v>
+        <v>112068010</v>
       </c>
       <c r="B9" t="n">
-        <v>88182</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,37 +1380,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1599</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjärnmyren (Tjärnmyren), Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469256</v>
+        <v>469452</v>
       </c>
       <c r="R9" t="n">
-        <v>7039724</v>
+        <v>7039596</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1449,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1508,54 +1467,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112370021</v>
+        <v>112068136</v>
       </c>
       <c r="B10" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>nybodarna Österulvsås, Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469287</v>
+        <v>469497</v>
       </c>
       <c r="R10" t="n">
-        <v>7039645</v>
+        <v>7039592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,17 +1533,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,27 +1553,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112370020</v>
+        <v>112370012</v>
       </c>
       <c r="B11" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469262</v>
+        <v>469631</v>
       </c>
       <c r="R11" t="n">
-        <v>7039652</v>
+        <v>7039391</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,17 +1634,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,15 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112370012</v>
+        <v>112370020</v>
       </c>
       <c r="B12" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469631</v>
+        <v>469262</v>
       </c>
       <c r="R12" t="n">
-        <v>7039391</v>
+        <v>7039652</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1740,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,6 +1774,112 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112370021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>nybodarna Österulvsås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>469287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039645</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42385-2023 artfynd.xlsx
+++ b/artfynd/A 42385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112067161</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112067971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370043</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112067953</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068136</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370012</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,8 +1940,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>